--- a/PREF_787.xlsx
+++ b/PREF_787.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nagu/Desktop/NVZ_SKD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6106BF38-1D68-C041-9E37-19693815DF80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163FF1B0-1313-314C-93D4-22951451ABDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="860" windowWidth="34200" windowHeight="21380" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="色分け設定" sheetId="1" r:id="rId1"/>
     <sheet name="SIMSLOT" sheetId="3" r:id="rId2"/>
     <sheet name="emp_no" sheetId="4" r:id="rId3"/>
-    <sheet name="抽出変換設定" sheetId="2" r:id="rId4"/>
+    <sheet name="SKD抽出用" sheetId="5" r:id="rId4"/>
+    <sheet name="抽出変換設定" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="emp_no" localSheetId="2">emp_no!$A$1:$I$103</definedName>
@@ -58,8 +59,30 @@
 </connections>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="455">
   <si>
     <t>対象文字列</t>
   </si>
@@ -1413,13 +1436,112 @@
   </si>
   <si>
     <t>36973</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">名簿にある乗員だけのリストを作成するには以下の職員番号をコピペしてJasper Reportでスケジュール抽出してください。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">その際[FLEET]（350,787など）を選ぶのを忘れないでください。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>全乗員のスケジュールを整形する場合はFLEETのみ選択でOKです。（時間がかかります。）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+下のセルは自動計算です。絶対に書き換えないでください。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t xml:space="preserve">メイボニアル </t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t xml:space="preserve">ジョウインダケノリストヲ </t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t xml:space="preserve">サクセイスルニハ </t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t xml:space="preserve">イカノ </t>
+    </rPh>
+    <rPh sb="23" eb="27">
+      <t xml:space="preserve">ショクインバンゴウヲ </t>
+    </rPh>
+    <rPh sb="85" eb="86">
+      <t xml:space="preserve">エラブノヲ </t>
+    </rPh>
+    <rPh sb="89" eb="90">
+      <t xml:space="preserve">ワスレナイデクダサイ </t>
+    </rPh>
+    <rPh sb="100" eb="103">
+      <t xml:space="preserve">ゼンジョウインヲ </t>
+    </rPh>
+    <rPh sb="111" eb="113">
+      <t xml:space="preserve">セイケイスルバアイハ </t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t xml:space="preserve">センタクデ </t>
+    </rPh>
+    <rPh sb="134" eb="136">
+      <t xml:space="preserve">ジカンガカカリマス </t>
+    </rPh>
+    <rPh sb="145" eb="146">
+      <t xml:space="preserve">シタノセルハ </t>
+    </rPh>
+    <rPh sb="150" eb="154">
+      <t xml:space="preserve">ジドウケイサンデス </t>
+    </rPh>
+    <rPh sb="157" eb="159">
+      <t xml:space="preserve">ゼッタイニカキカエナイデクダサイ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>"=TEXTJOIN(",", TRUE, IF(emp_no!C2:C103&lt;&gt;"", "000"&amp;emp_no!C2:C103, ""))"</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>復帰用</t>
+    <rPh sb="0" eb="3">
+      <t xml:space="preserve">フッキヨウ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>変更禁止</t>
+    <rPh sb="0" eb="4">
+      <t xml:space="preserve">ヘンコウキンシ </t>
+    </rPh>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1442,8 +1564,37 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1540,6 +1691,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1553,7 +1710,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1579,6 +1736,16 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -4965,6 +5132,82 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17283296-D1A1-9640-95FC-05D928A99483}">
+  <dimension ref="A1:W4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1" spans="1:23" ht="118" customHeight="1">
+      <c r="A1" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+    </row>
+    <row r="2" spans="1:23" ht="221" customHeight="1">
+      <c r="A2" s="19" t="str" cm="1">
+        <f t="array" ref="A2">_xlfn.TEXTJOIN(",", TRUE, IF(emp_no!C2:C103&lt;&gt;"", "000"&amp;emp_no!C2:C103, ""))</f>
+        <v>00041171,00041665,00049181,00042421,00041574,00041218,00044524,00045028,00041213,00037725,00041558,00038554,00038560,00037736,00039670,00036749,00040567,00041467,00038561,00040789,00049377,00037755,00037702,00037746,00037757,00037244,00048009,00049245,00067670,00067428,00067211,00067770,00041476,00067849,00037255,00040590,00049241,00049240,00048994,00038531,00039358,00067667,00040785,00039625,00067650,00048992,00041170,00041365,00067264,00041662,00067665,00039361,00039676,00043998,00037744,00041373,00044871,00036149,00042707,00041572,00038570,00043997,00041180,00041168,00040576,00041384,00036186,00045615,00038604,00038601,00053852,00053797,00053883,00053882,00053880,00053878,00041200,00053819,00053822,00053825,00053831,00053828,00053824,00053827,00053820,00053829,00043999,00048991,00044520,00041266,00043856,00053785,00045109,00050730,00051865,00051871,00051867,00051873,00051864,00041335,00049375,00036973</v>
+      </c>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+    </row>
+    <row r="3" spans="1:23">
+      <c r="Q3" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="R3" s="22" t="s">
+        <v>452</v>
+      </c>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+    </row>
+    <row r="4" spans="1:23">
+      <c r="Q4" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
